--- a/MU/Test upload format/Normal/2027 - 2028/Q1 27-28 .xlsx
+++ b/MU/Test upload format/Normal/2027 - 2028/Q1 27-28 .xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
     <t>SBIN0001235</t>
   </si>
   <si>
-    <t>2728CR701</t>
+    <t>CR1301</t>
   </si>
   <si>
     <t>100000</t>
@@ -215,7 +215,7 @@
     <t>SBIN0001234</t>
   </si>
   <si>
-    <t>2728CR702</t>
+    <t>CR1302</t>
   </si>
   <si>
     <t>AQPPL5</t>
@@ -227,7 +227,7 @@
     <t>CR703</t>
   </si>
   <si>
-    <t>2728CR703</t>
+    <t>CR1303</t>
   </si>
   <si>
     <t>200000</t>
@@ -245,49 +245,49 @@
     <t>CR704</t>
   </si>
   <si>
-    <t>2728CR704</t>
+    <t>CR1304</t>
   </si>
   <si>
     <t>CR705</t>
   </si>
   <si>
-    <t>2728CR705</t>
+    <t>CR1305</t>
   </si>
   <si>
     <t>CR706</t>
   </si>
   <si>
-    <t>2728CR706</t>
+    <t>CR1306</t>
   </si>
   <si>
     <t>CR707</t>
   </si>
   <si>
-    <t>2728CR707</t>
+    <t>CR1307</t>
   </si>
   <si>
     <t>CR708</t>
   </si>
   <si>
-    <t>2728CR708</t>
+    <t>CR1308</t>
   </si>
   <si>
     <t>CR709</t>
   </si>
   <si>
-    <t>2728CR709</t>
+    <t>CR1309</t>
   </si>
   <si>
     <t>CR710</t>
   </si>
   <si>
-    <t>2728CR710</t>
+    <t>CR1310</t>
   </si>
   <si>
     <t>CR711</t>
   </si>
   <si>
-    <t>2728CR711</t>
+    <t>CR1311</t>
   </si>
   <si>
     <t>T</t>
@@ -296,25 +296,25 @@
     <t>CR712</t>
   </si>
   <si>
-    <t>2728CR712</t>
+    <t>CR1312</t>
   </si>
   <si>
     <t>CR713</t>
   </si>
   <si>
-    <t>2728CR713</t>
+    <t>CR1313</t>
   </si>
   <si>
     <t>CR714</t>
   </si>
   <si>
-    <t>2728CR714</t>
+    <t>CR1314</t>
   </si>
   <si>
     <t>CR715</t>
   </si>
   <si>
-    <t>2728CR715</t>
+    <t>CR1315</t>
   </si>
   <si>
     <t>3</t>
@@ -323,7 +323,7 @@
     <t>CR716</t>
   </si>
   <si>
-    <t>2728CR716</t>
+    <t>CR1316</t>
   </si>
   <si>
     <t>4</t>
@@ -332,49 +332,49 @@
     <t>CR717</t>
   </si>
   <si>
-    <t>2728CR717</t>
+    <t>CR1317</t>
   </si>
   <si>
     <t>CR718</t>
   </si>
   <si>
-    <t>2728CR718</t>
+    <t>CR1318</t>
   </si>
   <si>
     <t>CR719</t>
   </si>
   <si>
-    <t>2728CR719</t>
+    <t>CR1319</t>
   </si>
   <si>
     <t>CR720</t>
   </si>
   <si>
-    <t>2728CR720</t>
+    <t>CR1320</t>
   </si>
   <si>
     <t>CR721</t>
   </si>
   <si>
-    <t>2728CR721</t>
+    <t>CR1321</t>
   </si>
   <si>
     <t>CR722</t>
   </si>
   <si>
-    <t>2728CR722</t>
+    <t>CR1322</t>
   </si>
   <si>
     <t>CR723</t>
   </si>
   <si>
-    <t>2728CR723</t>
+    <t>CR1323</t>
   </si>
   <si>
     <t>CR724</t>
   </si>
   <si>
-    <t>2728CR724</t>
+    <t>CR1324</t>
   </si>
 </sst>
 </file>
